--- a/data/syllabus.xlsx
+++ b/data/syllabus.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daviddl\Documents\EDUC\EDUC641_23F\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daviddl\Documents\EDUC\EDUC641_26F\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C4B4AF-0211-494B-8072-557AAFB18E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425"/>
+    <workbookView xWindow="3495" yWindow="390" windowWidth="20085" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,19 +144,19 @@
     <t>Unit</t>
   </si>
   <si>
-    <t>LSWR Ch 11 and 12  &lt;br&gt; [Evans 2020](https://www.newstatesman.com/uncategorized/2020/07/ra-fisher-and-science-hatred)</t>
-  </si>
-  <si>
     <t>LSWR Ch 2 and 3  &lt;br&gt; [Light, Singer &amp; Willet 1990, Ch. 2](./assignments/Light Singer Willett 1990.pdf)</t>
   </si>
   <si>
-    <t>LSWR Ch 6  &lt;br&gt; [Clayton 2020](https://nautil.us/how-eugenics-shaped-statistics-238014)</t>
+    <t>LSWR Ch 6</t>
+  </si>
+  <si>
+    <t>LSWR Ch 11 and 12 &lt;br&gt; [Clayton 2020](https://nautil.us/how-eugenics-shaped-statistics-238014) &lt;br&gt; [Evans 2020](https://www.newstatesman.com/uncategorized/2020/07/ra-fisher-and-science-hatred)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -520,7 +521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -564,7 +565,7 @@
         <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>17</v>
@@ -584,7 +585,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>18</v>
@@ -604,7 +605,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>6</v>
